--- a/config/Step7_指标需求清单.xlsx
+++ b/config/Step7_指标需求清单.xlsx
@@ -3202,7 +3202,7 @@
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>本季度末数</t>
+          <t>本年累计数</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
@@ -3272,7 +3272,7 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>本季度末数</t>
+          <t>本年累计数</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>本季度末数</t>
+          <t>本年累计数</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">

--- a/config/Step7_指标需求清单.xlsx
+++ b/config/Step7_指标需求清单.xlsx
@@ -1476,7 +1476,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>本年累计数</t>
+          <t>本季度数</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>本季度末数</t>
+          <t>本季度数</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
